--- a/models/llmcatelog.xlsx
+++ b/models/llmcatelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AFBB74-3739-EE49-BB94-C2D594F68504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21B017E-1E3D-F342-A3F3-C36EB3D456F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34220" yWindow="10800" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
   <si>
     <t>name</t>
   </si>
@@ -249,13 +249,7 @@
     <t>类型说明</t>
   </si>
   <si>
-    <t>input_fields</t>
-  </si>
-  <si>
     <t>input_view</t>
-  </si>
-  <si>
-    <t>输入字段</t>
   </si>
   <si>
     <t>输入显示</t>
@@ -707,10 +701,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
@@ -736,7 +730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -808,7 +802,7 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -816,32 +810,21 @@
         <v>74</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -855,13 +838,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C45:C318</xm:sqref>
+          <xm:sqref>C44:C317</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A978982F-96CB-474E-9DDC-FC7702131E75}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C44</xm:sqref>
+          <xm:sqref>C2:C43</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1094,7 +1077,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/models/llmcatelog.xlsx
+++ b/models/llmcatelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21B017E-1E3D-F342-A3F3-C36EB3D456F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB49AD7-5625-8042-AA04-4C8260515F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34220" yWindow="10800" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30100" yWindow="14180" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="88">
   <si>
     <t>name</t>
   </si>
@@ -274,6 +274,30 @@
   <si>
     <t>text</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assisant_message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>system_message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统消息格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户消息格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型消息格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -730,7 +754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -824,6 +848,39 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
         <v>80</v>
       </c>
     </row>

--- a/models/llmcatelog.xlsx
+++ b/models/llmcatelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB49AD7-5625-8042-AA04-4C8260515F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B487B13A-EDA8-DF42-BDA4-38B83B5132B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30100" yWindow="14180" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8720" yWindow="10540" windowWidth="40960" windowHeight="23400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="88">
   <si>
     <t>name</t>
   </si>
@@ -247,18 +247,6 @@
   </si>
   <si>
     <t>类型说明</t>
-  </si>
-  <si>
-    <t>input_view</t>
-  </si>
-  <si>
-    <t>输入显示</t>
-  </si>
-  <si>
-    <t>output_view</t>
-  </si>
-  <si>
-    <t>输出显示</t>
   </si>
   <si>
     <t>llmcatelog</t>
@@ -276,28 +264,44 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>user_message</t>
+    <t>hfid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>assisant_message</t>
+    <t>历史格式id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>system_message</t>
+    <t>ioid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>系统消息格式</t>
+    <t>hfid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>historyformat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>yes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用户消息格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模型消息格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>ioid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>uapiio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -725,10 +729,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
@@ -754,7 +758,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -826,62 +830,41 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -895,13 +878,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C44:C317</xm:sqref>
+          <xm:sqref>C39:C312</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A978982F-96CB-474E-9DDC-FC7702131E75}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C43</xm:sqref>
+          <xm:sqref>C2:C38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -993,17 +976,33 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="A2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1134,7 +1133,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/models/llmcatelog.xlsx
+++ b/models/llmcatelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B487B13A-EDA8-DF42-BDA4-38B83B5132B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83351853-6CA9-4D46-BB54-4C0F255A1FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8720" yWindow="10540" windowWidth="40960" windowHeight="23400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2200" windowWidth="40960" windowHeight="23400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>name</t>
   </si>
@@ -261,46 +261,6 @@
   </si>
   <si>
     <t>text</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hfid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>历史格式id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ioid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hfid</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>historyformat</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>yes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ioid</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>uapiio</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -758,7 +718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -833,40 +793,6 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>32</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>32</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -878,13 +804,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C39:C312</xm:sqref>
+          <xm:sqref>C37:C310</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A978982F-96CB-474E-9DDC-FC7702131E75}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C38</xm:sqref>
+          <xm:sqref>C2:C36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -955,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D73A0C9-9802-0C4C-A2B3-372B9ED806BE}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -973,35 +899,6 @@
       </c>
       <c r="E1" s="8" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
